--- a/employee_work_shift.xlsx
+++ b/employee_work_shift.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Time_Attendance_Machine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47872316-83EA-4A38-B8E9-0D68AB225DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E0D413-99B2-4088-8265-7C248501499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0AC6C86D-A7DA-4E94-9BF2-C4BD896917EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8374" uniqueCount="2588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8375" uniqueCount="2589">
   <si>
     <t>N</t>
   </si>
@@ -7804,7 +7804,10 @@
     <t>TỔ 6</t>
   </si>
   <si>
-    <t>6n2r</t>
+    <t>a</t>
+  </si>
+  <si>
+    <t>4n4r</t>
   </si>
 </sst>
 </file>
@@ -8344,7 +8347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EA6547-03D1-40DF-B606-2C4BD2F4B62F}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J1351"/>
+  <dimension ref="A1:J1357"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.7265625" style="13" customWidth="1"/>
@@ -14756,7 +14759,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="208" spans="1:10" hidden="1">
@@ -45627,11 +45630,16 @@
         <v>46098</v>
       </c>
     </row>
+    <row r="1357" spans="1:7">
+      <c r="E1357" s="13" t="s">
+        <v>2587</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1351" xr:uid="{04EA6547-03D1-40DF-B606-2C4BD2F4B62F}">
-    <filterColumn colId="1">
+    <filterColumn colId="9">
       <filters>
-        <filter val="232509037"/>
+        <filter val="6n2r"/>
       </filters>
     </filterColumn>
   </autoFilter>
